--- a/LubanConfig/Moba/Production/Datas/__tables__.xlsx
+++ b/LubanConfig/Moba/Production/Datas/__tables__.xlsx
@@ -1015,7 +1015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K41"/>
+  <dimension ref="A1:K40"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5"/>
   <cols>
     <col width="20.375" customWidth="1" style="3" min="2" max="2"/>
@@ -1349,12 +1349,12 @@
     <row r="9">
       <c r="B9" s="0" t="inlineStr">
         <is>
-          <t>SkillFlows</t>
+          <t>SkillLevelTables</t>
         </is>
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
-          <t>DRSkillFlows</t>
+          <t>DRSkillLevelTables</t>
         </is>
       </c>
       <c r="D9" s="0" t="b">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="E9" s="0" t="inlineStr">
         <is>
-          <t>skill_flows@skill_flows.xlsx</t>
+          <t>skill_level_tables@skill_level_tables.xlsx</t>
         </is>
       </c>
       <c r="F9" s="0" t="inlineStr">
@@ -1377,19 +1377,19 @@
       </c>
       <c r="K9" s="0" t="inlineStr">
         <is>
-          <t>skill_flows</t>
+          <t>skill_level_tables</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="0" t="inlineStr">
         <is>
-          <t>SkillLevelTables</t>
+          <t>Models</t>
         </is>
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
-          <t>DRSkillLevelTables</t>
+          <t>DRModels</t>
         </is>
       </c>
       <c r="D10" s="0" t="b">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="E10" s="0" t="inlineStr">
         <is>
-          <t>skill_level_tables@skill_level_tables.xlsx</t>
+          <t>models@models.xlsx</t>
         </is>
       </c>
       <c r="F10" s="0" t="inlineStr">
@@ -1412,19 +1412,19 @@
       </c>
       <c r="K10" s="0" t="inlineStr">
         <is>
-          <t>skill_level_tables</t>
+          <t>models</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="0" t="inlineStr">
         <is>
-          <t>Models</t>
+          <t>Buffs</t>
         </is>
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
-          <t>DRModels</t>
+          <t>DRBuffs</t>
         </is>
       </c>
       <c r="D11" s="0" t="b">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="E11" s="0" t="inlineStr">
         <is>
-          <t>models@models.xlsx</t>
+          <t>buffs@buffs.xlsx</t>
         </is>
       </c>
       <c r="F11" s="0" t="inlineStr">
@@ -1447,19 +1447,19 @@
       </c>
       <c r="K11" s="0" t="inlineStr">
         <is>
-          <t>models</t>
+          <t>buffs</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="0" t="inlineStr">
         <is>
-          <t>Buffs</t>
+          <t>ContinuousProcesses</t>
         </is>
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
-          <t>DRBuffs</t>
+          <t>DRContinuousProcesses</t>
         </is>
       </c>
       <c r="D12" s="0" t="b">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="E12" s="0" t="inlineStr">
         <is>
-          <t>buffs@buffs.xlsx</t>
+          <t>continuous_processes@continuous_processes.xlsx</t>
         </is>
       </c>
       <c r="F12" s="0" t="inlineStr">
@@ -1482,19 +1482,19 @@
       </c>
       <c r="K12" s="0" t="inlineStr">
         <is>
-          <t>buffs</t>
+          <t>continuous_processes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="0" t="inlineStr">
         <is>
-          <t>ContinuousProcesses</t>
+          <t>ProjectileLaunchers</t>
         </is>
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
-          <t>DRContinuousProcesses</t>
+          <t>DRProjectileLaunchers</t>
         </is>
       </c>
       <c r="D13" s="0" t="b">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="E13" s="0" t="inlineStr">
         <is>
-          <t>continuous_processes@continuous_processes.xlsx</t>
+          <t>projectile_launchers@projectile_launchers.xlsx</t>
         </is>
       </c>
       <c r="F13" s="0" t="inlineStr">
@@ -1517,19 +1517,19 @@
       </c>
       <c r="K13" s="0" t="inlineStr">
         <is>
-          <t>continuous_processes</t>
+          <t>projectile_launchers</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="0" t="inlineStr">
         <is>
-          <t>ProjectileLaunchers</t>
+          <t>Projectiles</t>
         </is>
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
-          <t>DRProjectileLaunchers</t>
+          <t>DRProjectiles</t>
         </is>
       </c>
       <c r="D14" s="0" t="b">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="E14" s="0" t="inlineStr">
         <is>
-          <t>projectile_launchers@projectile_launchers.xlsx</t>
+          <t>projectiles@projectiles.xlsx</t>
         </is>
       </c>
       <c r="F14" s="0" t="inlineStr">
@@ -1552,19 +1552,19 @@
       </c>
       <c r="K14" s="0" t="inlineStr">
         <is>
-          <t>projectile_launchers</t>
+          <t>projectiles</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="0" t="inlineStr">
         <is>
-          <t>Projectiles</t>
+          <t>Aoes</t>
         </is>
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
-          <t>DRProjectiles</t>
+          <t>DRAoes</t>
         </is>
       </c>
       <c r="D15" s="0" t="b">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="E15" s="0" t="inlineStr">
         <is>
-          <t>projectiles@projectiles.xlsx</t>
+          <t>aoes@aoes.xlsx</t>
         </is>
       </c>
       <c r="F15" s="0" t="inlineStr">
@@ -1587,19 +1587,19 @@
       </c>
       <c r="K15" s="0" t="inlineStr">
         <is>
-          <t>projectiles</t>
+          <t>aoes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="0" t="inlineStr">
         <is>
-          <t>Aoes</t>
+          <t>Emitters</t>
         </is>
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
-          <t>DRAoes</t>
+          <t>DREmitters</t>
         </is>
       </c>
       <c r="D16" s="0" t="b">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="E16" s="0" t="inlineStr">
         <is>
-          <t>aoes@aoes.xlsx</t>
+          <t>emitters@emitters.xlsx</t>
         </is>
       </c>
       <c r="F16" s="0" t="inlineStr">
@@ -1622,19 +1622,19 @@
       </c>
       <c r="K16" s="0" t="inlineStr">
         <is>
-          <t>aoes</t>
+          <t>emitters</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="0" t="inlineStr">
         <is>
-          <t>Emitters</t>
+          <t>Summons</t>
         </is>
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
-          <t>DREmitters</t>
+          <t>DRSummons</t>
         </is>
       </c>
       <c r="D17" s="0" t="b">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="E17" s="0" t="inlineStr">
         <is>
-          <t>emitters@emitters.xlsx</t>
+          <t>summons@summons.xlsx</t>
         </is>
       </c>
       <c r="F17" s="0" t="inlineStr">
@@ -1657,19 +1657,19 @@
       </c>
       <c r="K17" s="0" t="inlineStr">
         <is>
-          <t>emitters</t>
+          <t>summons</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="0" t="inlineStr">
         <is>
-          <t>Summons</t>
+          <t>SummonAttrInherits</t>
         </is>
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
-          <t>DRSummons</t>
+          <t>DRSummonAttrInherits</t>
         </is>
       </c>
       <c r="D18" s="0" t="b">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="E18" s="0" t="inlineStr">
         <is>
-          <t>summons@summons.xlsx</t>
+          <t>summon_attr_inherits@summon_attr_inherits.xlsx</t>
         </is>
       </c>
       <c r="F18" s="0" t="inlineStr">
@@ -1692,19 +1692,19 @@
       </c>
       <c r="K18" s="0" t="inlineStr">
         <is>
-          <t>summons</t>
+          <t>summon_attr_inherits</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="0" t="inlineStr">
         <is>
-          <t>SummonAttrInherits</t>
+          <t>ComponentTemplates</t>
         </is>
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
-          <t>DRSummonAttrInherits</t>
+          <t>DRComponentTemplates</t>
         </is>
       </c>
       <c r="D19" s="0" t="b">
@@ -1712,7 +1712,7 @@
       </c>
       <c r="E19" s="0" t="inlineStr">
         <is>
-          <t>summon_attr_inherits@summon_attr_inherits.xlsx</t>
+          <t>component_templates@component_templates.xlsx</t>
         </is>
       </c>
       <c r="F19" s="0" t="inlineStr">
@@ -1727,19 +1727,19 @@
       </c>
       <c r="K19" s="0" t="inlineStr">
         <is>
-          <t>summon_attr_inherits</t>
+          <t>component_templates</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="0" t="inlineStr">
         <is>
-          <t>ComponentTemplates</t>
+          <t>SkillButtonTemplates</t>
         </is>
       </c>
       <c r="C20" s="0" t="inlineStr">
         <is>
-          <t>DRComponentTemplates</t>
+          <t>DRSkillButtonTemplates</t>
         </is>
       </c>
       <c r="D20" s="0" t="b">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="E20" s="0" t="inlineStr">
         <is>
-          <t>component_templates@component_templates.xlsx</t>
+          <t>skill_button_templates@skill_button_templates.xlsx</t>
         </is>
       </c>
       <c r="F20" s="0" t="inlineStr">
@@ -1762,19 +1762,19 @@
       </c>
       <c r="K20" s="0" t="inlineStr">
         <is>
-          <t>component_templates</t>
+          <t>skill_button_templates</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="0" t="inlineStr">
         <is>
-          <t>SkillButtonTemplates</t>
+          <t>TagTemplates</t>
         </is>
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
-          <t>DRSkillButtonTemplates</t>
+          <t>DRTagTemplates</t>
         </is>
       </c>
       <c r="D21" s="0" t="b">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="E21" s="0" t="inlineStr">
         <is>
-          <t>skill_button_templates@skill_button_templates.xlsx</t>
+          <t>tag_templates@tag_templates.xlsx</t>
         </is>
       </c>
       <c r="F21" s="0" t="inlineStr">
@@ -1797,19 +1797,19 @@
       </c>
       <c r="K21" s="0" t="inlineStr">
         <is>
-          <t>skill_button_templates</t>
+          <t>tag_templates</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="0" t="inlineStr">
         <is>
-          <t>TagTemplates</t>
+          <t>ContinuousTagTemplates</t>
         </is>
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
-          <t>DRTagTemplates</t>
+          <t>DRContinuousTagTemplates</t>
         </is>
       </c>
       <c r="D22" s="0" t="b">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="E22" s="0" t="inlineStr">
         <is>
-          <t>tag_templates@tag_templates.xlsx</t>
+          <t>continuous_tag_templates@continuous_tag_templates.xlsx</t>
         </is>
       </c>
       <c r="F22" s="0" t="inlineStr">
@@ -1832,19 +1832,19 @@
       </c>
       <c r="K22" s="0" t="inlineStr">
         <is>
-          <t>tag_templates</t>
+          <t>continuous_tag_templates</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="0" t="inlineStr">
         <is>
-          <t>ContinuousTagTemplates</t>
+          <t>SearchQueryTemplates</t>
         </is>
       </c>
       <c r="C23" s="0" t="inlineStr">
         <is>
-          <t>DRContinuousTagTemplates</t>
+          <t>DRSearchQueryTemplates</t>
         </is>
       </c>
       <c r="D23" s="0" t="b">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="E23" s="0" t="inlineStr">
         <is>
-          <t>continuous_tag_templates@continuous_tag_templates.xlsx</t>
+          <t>search_query_templates@search_query_templates.xlsx</t>
         </is>
       </c>
       <c r="F23" s="0" t="inlineStr">
@@ -1867,19 +1867,19 @@
       </c>
       <c r="K23" s="0" t="inlineStr">
         <is>
-          <t>continuous_tag_templates</t>
+          <t>search_query_templates</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="0" t="inlineStr">
         <is>
-          <t>SearchQueryTemplates</t>
+          <t>SpawnSummonActionTemplates</t>
         </is>
       </c>
       <c r="C24" s="0" t="inlineStr">
         <is>
-          <t>DRSearchQueryTemplates</t>
+          <t>DRSpawnSummonActionTemplates</t>
         </is>
       </c>
       <c r="D24" s="0" t="b">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="E24" s="0" t="inlineStr">
         <is>
-          <t>search_query_templates@search_query_templates.xlsx</t>
+          <t>spawn_summon_action_templates@spawn_summon_action_templates.xlsx</t>
         </is>
       </c>
       <c r="F24" s="0" t="inlineStr">
@@ -1902,19 +1902,19 @@
       </c>
       <c r="K24" s="0" t="inlineStr">
         <is>
-          <t>search_query_templates</t>
+          <t>spawn_summon_action_templates</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="0" t="inlineStr">
         <is>
-          <t>SpawnSummonActionTemplates</t>
+          <t>PresentationTemplates</t>
         </is>
       </c>
       <c r="C25" s="0" t="inlineStr">
         <is>
-          <t>DRSpawnSummonActionTemplates</t>
+          <t>DRPresentationTemplates</t>
         </is>
       </c>
       <c r="D25" s="0" t="b">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="E25" s="0" t="inlineStr">
         <is>
-          <t>spawn_summon_action_templates@spawn_summon_action_templates.xlsx</t>
+          <t>presentation_templates@presentation_templates.xlsx</t>
         </is>
       </c>
       <c r="F25" s="0" t="inlineStr">
@@ -1937,19 +1937,19 @@
       </c>
       <c r="K25" s="0" t="inlineStr">
         <is>
-          <t>spawn_summon_action_templates</t>
+          <t>presentation_templates</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="0" t="inlineStr">
         <is>
-          <t>PresentationTemplates</t>
+          <t>BattleMaps</t>
         </is>
       </c>
       <c r="C26" s="0" t="inlineStr">
         <is>
-          <t>DRPresentationTemplates</t>
+          <t>DRBattleMaps</t>
         </is>
       </c>
       <c r="D26" s="0" t="b">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="E26" s="0" t="inlineStr">
         <is>
-          <t>presentation_templates@presentation_templates.xlsx</t>
+          <t>battle_maps@battle_maps.xlsx</t>
         </is>
       </c>
       <c r="F26" s="0" t="inlineStr">
@@ -1972,19 +1972,19 @@
       </c>
       <c r="K26" s="0" t="inlineStr">
         <is>
-          <t>presentation_templates</t>
+          <t>battle_maps</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="0" t="inlineStr">
         <is>
-          <t>BattleMaps</t>
+          <t>Gameplays</t>
         </is>
       </c>
       <c r="C27" s="0" t="inlineStr">
         <is>
-          <t>DRBattleMaps</t>
+          <t>DRGameplays</t>
         </is>
       </c>
       <c r="D27" s="0" t="b">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="E27" s="0" t="inlineStr">
         <is>
-          <t>battle_maps@battle_maps.xlsx</t>
+          <t>gameplays@gameplays.xlsx</t>
         </is>
       </c>
       <c r="F27" s="0" t="inlineStr">
@@ -2007,19 +2007,19 @@
       </c>
       <c r="K27" s="0" t="inlineStr">
         <is>
-          <t>battle_maps</t>
+          <t>gameplays</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="0" t="inlineStr">
         <is>
-          <t>Gameplays</t>
+          <t>MotionGroups</t>
         </is>
       </c>
       <c r="C28" s="0" t="inlineStr">
         <is>
-          <t>DRGameplays</t>
+          <t>DRMotionGroups</t>
         </is>
       </c>
       <c r="D28" s="0" t="b">
@@ -2027,7 +2027,7 @@
       </c>
       <c r="E28" s="0" t="inlineStr">
         <is>
-          <t>gameplays@gameplays.xlsx</t>
+          <t>motion_groups@motion_groups.xlsx</t>
         </is>
       </c>
       <c r="F28" s="0" t="inlineStr">
@@ -2042,19 +2042,19 @@
       </c>
       <c r="K28" s="0" t="inlineStr">
         <is>
-          <t>gameplays</t>
+          <t>motion_groups</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="0" t="inlineStr">
         <is>
-          <t>MotionGroups</t>
+          <t>Effects</t>
         </is>
       </c>
       <c r="C29" s="0" t="inlineStr">
         <is>
-          <t>DRMotionGroups</t>
+          <t>DREffects</t>
         </is>
       </c>
       <c r="D29" s="0" t="b">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="E29" s="0" t="inlineStr">
         <is>
-          <t>motion_groups@motion_groups.xlsx</t>
+          <t>effects@effects.xlsx</t>
         </is>
       </c>
       <c r="F29" s="0" t="inlineStr">
@@ -2077,19 +2077,19 @@
       </c>
       <c r="K29" s="0" t="inlineStr">
         <is>
-          <t>motion_groups</t>
+          <t>effects</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="0" t="inlineStr">
         <is>
-          <t>Effects</t>
+          <t>Brains</t>
         </is>
       </c>
       <c r="C30" s="0" t="inlineStr">
         <is>
-          <t>DREffects</t>
+          <t>DRBrains</t>
         </is>
       </c>
       <c r="D30" s="0" t="b">
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E30" s="0" t="inlineStr">
         <is>
-          <t>effects@effects.xlsx</t>
+          <t>brains@brains.xlsx</t>
         </is>
       </c>
       <c r="F30" s="0" t="inlineStr">
         <is>
-          <t>Id</t>
+          <t>BrainId</t>
         </is>
       </c>
       <c r="H30" s="0" t="inlineStr">
@@ -2112,19 +2112,19 @@
       </c>
       <c r="K30" s="0" t="inlineStr">
         <is>
-          <t>effects</t>
+          <t>brains</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="0" t="inlineStr">
         <is>
-          <t>Brains</t>
+          <t>ResourceActorStateMachines</t>
         </is>
       </c>
       <c r="C31" s="0" t="inlineStr">
         <is>
-          <t>DRBrains</t>
+          <t>DRResourceActorStateMachines</t>
         </is>
       </c>
       <c r="D31" s="0" t="b">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="E31" s="0" t="inlineStr">
         <is>
-          <t>brains@brains.xlsx</t>
+          <t>actor_state_machines@actor_state_machines.xlsx</t>
         </is>
       </c>
       <c r="F31" s="0" t="inlineStr">
         <is>
-          <t>BrainId</t>
+          <t>RowId</t>
         </is>
       </c>
       <c r="H31" s="0" t="inlineStr">
@@ -2147,19 +2147,19 @@
       </c>
       <c r="K31" s="0" t="inlineStr">
         <is>
-          <t>brains</t>
+          <t>actor_state_machines</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="0" t="inlineStr">
         <is>
-          <t>ResourceActorStateMachines</t>
+          <t>ResourceAttributetemplates</t>
         </is>
       </c>
       <c r="C32" s="0" t="inlineStr">
         <is>
-          <t>DRResourceActorStateMachines</t>
+          <t>DRResourceAttributetemplates</t>
         </is>
       </c>
       <c r="D32" s="0" t="b">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="E32" s="0" t="inlineStr">
         <is>
-          <t>actor_state_machines@actor_state_machines.xlsx</t>
+          <t>attributetemplates@attributetemplates.xlsx</t>
         </is>
       </c>
       <c r="F32" s="0" t="inlineStr">
         <is>
-          <t>RowId</t>
+          <t>Code</t>
         </is>
       </c>
       <c r="H32" s="0" t="inlineStr">
@@ -2182,19 +2182,19 @@
       </c>
       <c r="K32" s="0" t="inlineStr">
         <is>
-          <t>actor_state_machines</t>
+          <t>attributetemplates</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="0" t="inlineStr">
         <is>
-          <t>ResourceAttributetemplates</t>
+          <t>ResourceBattleStart</t>
         </is>
       </c>
       <c r="C33" s="0" t="inlineStr">
         <is>
-          <t>DRResourceAttributetemplates</t>
+          <t>DRResourceBattleStart</t>
         </is>
       </c>
       <c r="D33" s="0" t="b">
@@ -2202,12 +2202,12 @@
       </c>
       <c r="E33" s="0" t="inlineStr">
         <is>
-          <t>attributetemplates@attributetemplates.xlsx</t>
+          <t>battle_start@battle_start.xlsx</t>
         </is>
       </c>
       <c r="F33" s="0" t="inlineStr">
         <is>
-          <t>Code</t>
+          <t>RowId</t>
         </is>
       </c>
       <c r="H33" s="0" t="inlineStr">
@@ -2217,19 +2217,19 @@
       </c>
       <c r="K33" s="0" t="inlineStr">
         <is>
-          <t>attributetemplates</t>
+          <t>battle_start</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="0" t="inlineStr">
         <is>
-          <t>ResourceBattleStart</t>
+          <t>ResourceCharacterHfsm</t>
         </is>
       </c>
       <c r="C34" s="0" t="inlineStr">
         <is>
-          <t>DRResourceBattleStart</t>
+          <t>DRResourceCharacterHfsm</t>
         </is>
       </c>
       <c r="D34" s="0" t="b">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="E34" s="0" t="inlineStr">
         <is>
-          <t>battle_start@battle_start.xlsx</t>
+          <t>character_hfsm@character_hfsm.xlsx</t>
         </is>
       </c>
       <c r="F34" s="0" t="inlineStr">
@@ -2252,19 +2252,19 @@
       </c>
       <c r="K34" s="0" t="inlineStr">
         <is>
-          <t>battle_start</t>
+          <t>character_hfsm</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="0" t="inlineStr">
         <is>
-          <t>ResourceCharacterHfsm</t>
+          <t>ResourceCharacterViewActions</t>
         </is>
       </c>
       <c r="C35" s="0" t="inlineStr">
         <is>
-          <t>DRResourceCharacterHfsm</t>
+          <t>DRResourceCharacterViewActions</t>
         </is>
       </c>
       <c r="D35" s="0" t="b">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="E35" s="0" t="inlineStr">
         <is>
-          <t>character_hfsm@character_hfsm.xlsx</t>
+          <t>character_view_actions@character_view_actions.xlsx</t>
         </is>
       </c>
       <c r="F35" s="0" t="inlineStr">
@@ -2287,19 +2287,19 @@
       </c>
       <c r="K35" s="0" t="inlineStr">
         <is>
-          <t>character_hfsm</t>
+          <t>character_view_actions</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="0" t="inlineStr">
         <is>
-          <t>ResourceCharacterViewActions</t>
+          <t>ResourceDemoTbitem</t>
         </is>
       </c>
       <c r="C36" s="0" t="inlineStr">
         <is>
-          <t>DRResourceCharacterViewActions</t>
+          <t>DRResourceDemoTbitem</t>
         </is>
       </c>
       <c r="D36" s="0" t="b">
@@ -2307,12 +2307,12 @@
       </c>
       <c r="E36" s="0" t="inlineStr">
         <is>
-          <t>character_view_actions@character_view_actions.xlsx</t>
+          <t>demo_tbitem@demo_tbitem.xlsx</t>
         </is>
       </c>
       <c r="F36" s="0" t="inlineStr">
         <is>
-          <t>RowId</t>
+          <t>id</t>
         </is>
       </c>
       <c r="H36" s="0" t="inlineStr">
@@ -2322,19 +2322,19 @@
       </c>
       <c r="K36" s="0" t="inlineStr">
         <is>
-          <t>character_view_actions</t>
+          <t>demo_tbitem</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="0" t="inlineStr">
         <is>
-          <t>ResourceDemoTbitem</t>
+          <t>ResourceDtbuff</t>
         </is>
       </c>
       <c r="C37" s="0" t="inlineStr">
         <is>
-          <t>DRResourceDemoTbitem</t>
+          <t>DRResourceDtbuff</t>
         </is>
       </c>
       <c r="D37" s="0" t="b">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="E37" s="0" t="inlineStr">
         <is>
-          <t>demo_tbitem@demo_tbitem.xlsx</t>
+          <t>dtbuff@dtbuff.xlsx</t>
         </is>
       </c>
       <c r="F37" s="0" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>Id</t>
         </is>
       </c>
       <c r="H37" s="0" t="inlineStr">
@@ -2357,19 +2357,19 @@
       </c>
       <c r="K37" s="0" t="inlineStr">
         <is>
-          <t>demo_tbitem</t>
+          <t>dtbuff</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="0" t="inlineStr">
         <is>
-          <t>ResourceDtbuff</t>
+          <t>ResourceEffectPlans</t>
         </is>
       </c>
       <c r="C38" s="0" t="inlineStr">
         <is>
-          <t>DRResourceDtbuff</t>
+          <t>DRResourceEffectPlans</t>
         </is>
       </c>
       <c r="D38" s="0" t="b">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="E38" s="0" t="inlineStr">
         <is>
-          <t>dtbuff@dtbuff.xlsx</t>
+          <t>effect_plans@effect_plans.xlsx</t>
         </is>
       </c>
       <c r="F38" s="0" t="inlineStr">
         <is>
-          <t>Id</t>
+          <t>RowId</t>
         </is>
       </c>
       <c r="H38" s="0" t="inlineStr">
@@ -2392,19 +2392,19 @@
       </c>
       <c r="K38" s="0" t="inlineStr">
         <is>
-          <t>dtbuff</t>
+          <t>effect_plans</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="B39" s="0" t="inlineStr">
         <is>
-          <t>ResourceEffectPlans</t>
+          <t>ResourceOngoingEffects</t>
         </is>
       </c>
       <c r="C39" s="0" t="inlineStr">
         <is>
-          <t>DRResourceEffectPlans</t>
+          <t>DRResourceOngoingEffects</t>
         </is>
       </c>
       <c r="D39" s="0" t="b">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="E39" s="0" t="inlineStr">
         <is>
-          <t>effect_plans@effect_plans.xlsx</t>
+          <t>ongoing_effects@ongoing_effects.xlsx</t>
         </is>
       </c>
       <c r="F39" s="0" t="inlineStr">
         <is>
-          <t>RowId</t>
+          <t>Id</t>
         </is>
       </c>
       <c r="H39" s="0" t="inlineStr">
@@ -2427,19 +2427,19 @@
       </c>
       <c r="K39" s="0" t="inlineStr">
         <is>
-          <t>effect_plans</t>
+          <t>ongoing_effects</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="B40" s="0" t="inlineStr">
         <is>
-          <t>ResourceOngoingEffects</t>
+          <t>AbilityNodes</t>
         </is>
       </c>
       <c r="C40" s="0" t="inlineStr">
         <is>
-          <t>DRResourceOngoingEffects</t>
+          <t>DRAbilityNodes</t>
         </is>
       </c>
       <c r="D40" s="0" t="b">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="E40" s="0" t="inlineStr">
         <is>
-          <t>ongoing_effects@ongoing_effects.xlsx</t>
+          <t>ability_nodes@ability_nodes.xlsx</t>
         </is>
       </c>
       <c r="F40" s="0" t="inlineStr">
@@ -2461,41 +2461,6 @@
         </is>
       </c>
       <c r="K40" s="0" t="inlineStr">
-        <is>
-          <t>ongoing_effects</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="0" t="inlineStr">
-        <is>
-          <t>AbilityNodes</t>
-        </is>
-      </c>
-      <c r="C41" s="0" t="inlineStr">
-        <is>
-          <t>DRAbilityNodes</t>
-        </is>
-      </c>
-      <c r="D41" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E41" s="0" t="inlineStr">
-        <is>
-          <t>ability_nodes@ability_nodes.xlsx</t>
-        </is>
-      </c>
-      <c r="F41" s="0" t="inlineStr">
-        <is>
-          <t>Id</t>
-        </is>
-      </c>
-      <c r="H41" s="0" t="inlineStr">
-        <is>
-          <t>c,s,e</t>
-        </is>
-      </c>
-      <c r="K41" s="0" t="inlineStr">
         <is>
           <t>ability_nodes</t>
         </is>

--- a/LubanConfig/Moba/Production/Datas/__tables__.xlsx
+++ b/LubanConfig/Moba/Production/Datas/__tables__.xlsx
@@ -169,7 +169,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill/>
     </fill>
@@ -360,6 +360,11 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F1F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -619,7 +624,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -630,6 +635,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1140,6 +1148,16 @@
           <t>##</t>
         </is>
       </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>完整表或类型名，包含命名空间。</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>表记录的值类型。</t>
+        </is>
+      </c>
       <c r="D3" s="1" t="inlineStr">
         <is>
           <t>false时取已有定义，true为从excel标题头和属性栏读取定义</t>
@@ -1163,6 +1181,16 @@
       <c r="H3" s="1" t="inlineStr">
         <is>
           <t>取值c|s|e，可以有多个，以逗号','分隔。空则表示属于所有分组</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>供 Luban 读取的类型说明。</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>类型附加标签。</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
@@ -1187,7 +1215,7 @@
       </c>
       <c r="E4" s="0" t="inlineStr">
         <is>
-          <t>characters@characters.xlsx</t>
+          <t>角色@J-角色表.xlsx</t>
         </is>
       </c>
       <c r="F4" s="0" t="inlineStr">
@@ -1222,7 +1250,7 @@
       </c>
       <c r="E5" s="0" t="inlineStr">
         <is>
-          <t>attribute_templates@attribute_templates.xlsx</t>
+          <t>属性模板@J-角色表.xlsx</t>
         </is>
       </c>
       <c r="F5" s="0" t="inlineStr">
@@ -1257,7 +1285,7 @@
       </c>
       <c r="E6" s="0" t="inlineStr">
         <is>
-          <t>attr_types@attr_types.xlsx</t>
+          <t>属性类型@J-角色表.xlsx</t>
         </is>
       </c>
       <c r="F6" s="0" t="inlineStr">
@@ -1292,7 +1320,7 @@
       </c>
       <c r="E7" s="0" t="inlineStr">
         <is>
-          <t>skills@skills.xlsx</t>
+          <t>技能@J-技能表.xlsx</t>
         </is>
       </c>
       <c r="F7" s="0" t="inlineStr">
@@ -1327,7 +1355,7 @@
       </c>
       <c r="E8" s="0" t="inlineStr">
         <is>
-          <t>passive_skills@passive_skills.xlsx</t>
+          <t>被动技能@J-技能表.xlsx</t>
         </is>
       </c>
       <c r="F8" s="0" t="inlineStr">
@@ -1362,7 +1390,7 @@
       </c>
       <c r="E9" s="0" t="inlineStr">
         <is>
-          <t>skill_level_tables@skill_level_tables.xlsx</t>
+          <t>技能等级@J-技能表.xlsx</t>
         </is>
       </c>
       <c r="F9" s="0" t="inlineStr">
@@ -1397,7 +1425,7 @@
       </c>
       <c r="E10" s="0" t="inlineStr">
         <is>
-          <t>models@models.xlsx</t>
+          <t>模型资源@M-模型表.xlsx</t>
         </is>
       </c>
       <c r="F10" s="0" t="inlineStr">
@@ -1432,7 +1460,7 @@
       </c>
       <c r="E11" s="0" t="inlineStr">
         <is>
-          <t>buffs@buffs.xlsx</t>
+          <t>Buff@J-效果表.xlsx</t>
         </is>
       </c>
       <c r="F11" s="0" t="inlineStr">
@@ -1467,7 +1495,7 @@
       </c>
       <c r="E12" s="0" t="inlineStr">
         <is>
-          <t>continuous_processes@continuous_processes.xlsx</t>
+          <t>持续流程@J-效果表.xlsx</t>
         </is>
       </c>
       <c r="F12" s="0" t="inlineStr">
@@ -1502,7 +1530,7 @@
       </c>
       <c r="E13" s="0" t="inlineStr">
         <is>
-          <t>projectile_launchers@projectile_launchers.xlsx</t>
+          <t>投射发射器@J-投射物表.xlsx</t>
         </is>
       </c>
       <c r="F13" s="0" t="inlineStr">
@@ -1537,7 +1565,7 @@
       </c>
       <c r="E14" s="0" t="inlineStr">
         <is>
-          <t>projectiles@projectiles.xlsx</t>
+          <t>投射物@J-投射物表.xlsx</t>
         </is>
       </c>
       <c r="F14" s="0" t="inlineStr">
@@ -1572,7 +1600,7 @@
       </c>
       <c r="E15" s="0" t="inlineStr">
         <is>
-          <t>aoes@aoes.xlsx</t>
+          <t>区域@J-投射物表.xlsx</t>
         </is>
       </c>
       <c r="F15" s="0" t="inlineStr">
@@ -1607,7 +1635,7 @@
       </c>
       <c r="E16" s="0" t="inlineStr">
         <is>
-          <t>emitters@emitters.xlsx</t>
+          <t>发射器@J-投射物表.xlsx</t>
         </is>
       </c>
       <c r="F16" s="0" t="inlineStr">
@@ -1642,7 +1670,7 @@
       </c>
       <c r="E17" s="0" t="inlineStr">
         <is>
-          <t>summons@summons.xlsx</t>
+          <t>召唤物@J-召唤物表.xlsx</t>
         </is>
       </c>
       <c r="F17" s="0" t="inlineStr">
@@ -1677,7 +1705,7 @@
       </c>
       <c r="E18" s="0" t="inlineStr">
         <is>
-          <t>summon_attr_inherits@summon_attr_inherits.xlsx</t>
+          <t>召唤属性继承@J-召唤物表.xlsx</t>
         </is>
       </c>
       <c r="F18" s="0" t="inlineStr">
@@ -1712,7 +1740,7 @@
       </c>
       <c r="E19" s="0" t="inlineStr">
         <is>
-          <t>component_templates@component_templates.xlsx</t>
+          <t>组件模板@J-效果表.xlsx</t>
         </is>
       </c>
       <c r="F19" s="0" t="inlineStr">
@@ -1747,7 +1775,7 @@
       </c>
       <c r="E20" s="0" t="inlineStr">
         <is>
-          <t>skill_button_templates@skill_button_templates.xlsx</t>
+          <t>技能按钮与瞄准@J-技能表现表.xlsx</t>
         </is>
       </c>
       <c r="F20" s="0" t="inlineStr">
@@ -1769,12 +1797,12 @@
     <row r="21">
       <c r="B21" s="0" t="inlineStr">
         <is>
-          <t>TagTemplates</t>
+          <t>SearchQueryTemplates</t>
         </is>
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
-          <t>DRTagTemplates</t>
+          <t>DRSearchQueryTemplates</t>
         </is>
       </c>
       <c r="D21" s="0" t="b">
@@ -1782,7 +1810,7 @@
       </c>
       <c r="E21" s="0" t="inlineStr">
         <is>
-          <t>tag_templates@tag_templates.xlsx</t>
+          <t>目标查询@J-技能表.xlsx</t>
         </is>
       </c>
       <c r="F21" s="0" t="inlineStr">
@@ -1797,19 +1825,19 @@
       </c>
       <c r="K21" s="0" t="inlineStr">
         <is>
-          <t>tag_templates</t>
+          <t>search_query_templates</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="0" t="inlineStr">
         <is>
-          <t>ContinuousTagTemplates</t>
+          <t>SpawnSummonActionTemplates</t>
         </is>
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
-          <t>DRContinuousTagTemplates</t>
+          <t>DRSpawnSummonActionTemplates</t>
         </is>
       </c>
       <c r="D22" s="0" t="b">
@@ -1817,7 +1845,7 @@
       </c>
       <c r="E22" s="0" t="inlineStr">
         <is>
-          <t>continuous_tag_templates@continuous_tag_templates.xlsx</t>
+          <t>召唤动作模板@J-召唤物表.xlsx</t>
         </is>
       </c>
       <c r="F22" s="0" t="inlineStr">
@@ -1832,19 +1860,19 @@
       </c>
       <c r="K22" s="0" t="inlineStr">
         <is>
-          <t>continuous_tag_templates</t>
+          <t>spawn_summon_action_templates</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="0" t="inlineStr">
         <is>
-          <t>SearchQueryTemplates</t>
+          <t>PresentationTemplates</t>
         </is>
       </c>
       <c r="C23" s="0" t="inlineStr">
         <is>
-          <t>DRSearchQueryTemplates</t>
+          <t>DRPresentationTemplates</t>
         </is>
       </c>
       <c r="D23" s="0" t="b">
@@ -1852,7 +1880,7 @@
       </c>
       <c r="E23" s="0" t="inlineStr">
         <is>
-          <t>search_query_templates@search_query_templates.xlsx</t>
+          <t>特效表现模板@T-特效表.xlsx</t>
         </is>
       </c>
       <c r="F23" s="0" t="inlineStr">
@@ -1867,19 +1895,19 @@
       </c>
       <c r="K23" s="0" t="inlineStr">
         <is>
-          <t>search_query_templates</t>
+          <t>presentation_templates</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="0" t="inlineStr">
         <is>
-          <t>SpawnSummonActionTemplates</t>
+          <t>BattleMaps</t>
         </is>
       </c>
       <c r="C24" s="0" t="inlineStr">
         <is>
-          <t>DRSpawnSummonActionTemplates</t>
+          <t>DRBattleMaps</t>
         </is>
       </c>
       <c r="D24" s="0" t="b">
@@ -1887,7 +1915,7 @@
       </c>
       <c r="E24" s="0" t="inlineStr">
         <is>
-          <t>spawn_summon_action_templates@spawn_summon_action_templates.xlsx</t>
+          <t>战斗地图@J-战斗场景表.xlsx</t>
         </is>
       </c>
       <c r="F24" s="0" t="inlineStr">
@@ -1902,19 +1930,19 @@
       </c>
       <c r="K24" s="0" t="inlineStr">
         <is>
-          <t>spawn_summon_action_templates</t>
+          <t>battle_maps</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="0" t="inlineStr">
         <is>
-          <t>PresentationTemplates</t>
+          <t>Gameplays</t>
         </is>
       </c>
       <c r="C25" s="0" t="inlineStr">
         <is>
-          <t>DRPresentationTemplates</t>
+          <t>DRGameplays</t>
         </is>
       </c>
       <c r="D25" s="0" t="b">
@@ -1922,7 +1950,7 @@
       </c>
       <c r="E25" s="0" t="inlineStr">
         <is>
-          <t>presentation_templates@presentation_templates.xlsx</t>
+          <t>玩法@J-战斗场景表.xlsx</t>
         </is>
       </c>
       <c r="F25" s="0" t="inlineStr">
@@ -1937,19 +1965,19 @@
       </c>
       <c r="K25" s="0" t="inlineStr">
         <is>
-          <t>presentation_templates</t>
+          <t>gameplays</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="0" t="inlineStr">
         <is>
-          <t>BattleMaps</t>
+          <t>MotionGroups</t>
         </is>
       </c>
       <c r="C26" s="0" t="inlineStr">
         <is>
-          <t>DRBattleMaps</t>
+          <t>DRMotionGroups</t>
         </is>
       </c>
       <c r="D26" s="0" t="b">
@@ -1957,7 +1985,7 @@
       </c>
       <c r="E26" s="0" t="inlineStr">
         <is>
-          <t>battle_maps@battle_maps.xlsx</t>
+          <t>运动组@J-效果表.xlsx</t>
         </is>
       </c>
       <c r="F26" s="0" t="inlineStr">
@@ -1972,19 +2000,19 @@
       </c>
       <c r="K26" s="0" t="inlineStr">
         <is>
-          <t>battle_maps</t>
+          <t>motion_groups</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="0" t="inlineStr">
         <is>
-          <t>Gameplays</t>
+          <t>Brains</t>
         </is>
       </c>
       <c r="C27" s="0" t="inlineStr">
         <is>
-          <t>DRGameplays</t>
+          <t>DRBrains</t>
         </is>
       </c>
       <c r="D27" s="0" t="b">
@@ -1992,12 +2020,12 @@
       </c>
       <c r="E27" s="0" t="inlineStr">
         <is>
-          <t>gameplays@gameplays.xlsx</t>
+          <t>AI脑@J-角色表.xlsx</t>
         </is>
       </c>
       <c r="F27" s="0" t="inlineStr">
         <is>
-          <t>Id</t>
+          <t>BrainId</t>
         </is>
       </c>
       <c r="H27" s="0" t="inlineStr">
@@ -2007,19 +2035,19 @@
       </c>
       <c r="K27" s="0" t="inlineStr">
         <is>
-          <t>gameplays</t>
+          <t>brains</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="0" t="inlineStr">
         <is>
-          <t>MotionGroups</t>
+          <t>ResourceBattleStart</t>
         </is>
       </c>
       <c r="C28" s="0" t="inlineStr">
         <is>
-          <t>DRMotionGroups</t>
+          <t>DRResourceBattleStart</t>
         </is>
       </c>
       <c r="D28" s="0" t="b">
@@ -2027,12 +2055,12 @@
       </c>
       <c r="E28" s="0" t="inlineStr">
         <is>
-          <t>motion_groups@motion_groups.xlsx</t>
+          <t>战斗开局@J-战斗场景表.xlsx</t>
         </is>
       </c>
       <c r="F28" s="0" t="inlineStr">
         <is>
-          <t>Id</t>
+          <t>RowId</t>
         </is>
       </c>
       <c r="H28" s="0" t="inlineStr">
@@ -2042,19 +2070,19 @@
       </c>
       <c r="K28" s="0" t="inlineStr">
         <is>
-          <t>motion_groups</t>
+          <t>battle_start</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="0" t="inlineStr">
         <is>
-          <t>Effects</t>
+          <t>ResourceCharacterViewActions</t>
         </is>
       </c>
       <c r="C29" s="0" t="inlineStr">
         <is>
-          <t>DREffects</t>
+          <t>DRResourceCharacterViewActions</t>
         </is>
       </c>
       <c r="D29" s="0" t="b">
@@ -2062,12 +2090,12 @@
       </c>
       <c r="E29" s="0" t="inlineStr">
         <is>
-          <t>effects@effects.xlsx</t>
+          <t>角色动画动作@M-模型表.xlsx</t>
         </is>
       </c>
       <c r="F29" s="0" t="inlineStr">
         <is>
-          <t>Id</t>
+          <t>RowId</t>
         </is>
       </c>
       <c r="H29" s="0" t="inlineStr">
@@ -2077,19 +2105,19 @@
       </c>
       <c r="K29" s="0" t="inlineStr">
         <is>
-          <t>effects</t>
+          <t>character_view_actions</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="0" t="inlineStr">
         <is>
-          <t>Brains</t>
+          <t>AbilityNodes</t>
         </is>
       </c>
       <c r="C30" s="0" t="inlineStr">
         <is>
-          <t>DRBrains</t>
+          <t>DRAbilityNodes</t>
         </is>
       </c>
       <c r="D30" s="0" t="b">
@@ -2097,12 +2125,12 @@
       </c>
       <c r="E30" s="0" t="inlineStr">
         <is>
-          <t>brains@brains.xlsx</t>
+          <t>Ability节点@J-资源节点表.xlsx</t>
         </is>
       </c>
       <c r="F30" s="0" t="inlineStr">
         <is>
-          <t>BrainId</t>
+          <t>Id</t>
         </is>
       </c>
       <c r="H30" s="0" t="inlineStr">
@@ -2112,19 +2140,19 @@
       </c>
       <c r="K30" s="0" t="inlineStr">
         <is>
-          <t>brains</t>
+          <t>ability_nodes</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="0" t="inlineStr">
         <is>
-          <t>ResourceActorStateMachines</t>
+          <t>Vfx</t>
         </is>
       </c>
       <c r="C31" s="0" t="inlineStr">
         <is>
-          <t>DRResourceActorStateMachines</t>
+          <t>DRVfx</t>
         </is>
       </c>
       <c r="D31" s="0" t="b">
@@ -2132,12 +2160,12 @@
       </c>
       <c r="E31" s="0" t="inlineStr">
         <is>
-          <t>actor_state_machines@actor_state_machines.xlsx</t>
+          <t>特效资源@T-特效表.xlsx</t>
         </is>
       </c>
       <c r="F31" s="0" t="inlineStr">
         <is>
-          <t>RowId</t>
+          <t>Id</t>
         </is>
       </c>
       <c r="H31" s="0" t="inlineStr">
@@ -2147,19 +2175,19 @@
       </c>
       <c r="K31" s="0" t="inlineStr">
         <is>
-          <t>actor_state_machines</t>
+          <t>vfx</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="0" t="inlineStr">
         <is>
-          <t>ResourceAttributetemplates</t>
+          <t>ModifierTemplates</t>
         </is>
       </c>
       <c r="C32" s="0" t="inlineStr">
         <is>
-          <t>DRResourceAttributetemplates</t>
+          <t>DRModifierTemplates</t>
         </is>
       </c>
       <c r="D32" s="0" t="b">
@@ -2167,12 +2195,12 @@
       </c>
       <c r="E32" s="0" t="inlineStr">
         <is>
-          <t>attributetemplates@attributetemplates.xlsx</t>
+          <t>修饰器定义@J-效果表.xlsx</t>
         </is>
       </c>
       <c r="F32" s="0" t="inlineStr">
         <is>
-          <t>Code</t>
+          <t>Id</t>
         </is>
       </c>
       <c r="H32" s="0" t="inlineStr">
@@ -2182,19 +2210,19 @@
       </c>
       <c r="K32" s="0" t="inlineStr">
         <is>
-          <t>attributetemplates</t>
+          <t>modifier_templates</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="0" t="inlineStr">
         <is>
-          <t>ResourceBattleStart</t>
+          <t>TagDefinitions</t>
         </is>
       </c>
       <c r="C33" s="0" t="inlineStr">
         <is>
-          <t>DRResourceBattleStart</t>
+          <t>DRTagDefinitions</t>
         </is>
       </c>
       <c r="D33" s="0" t="b">
@@ -2202,12 +2230,12 @@
       </c>
       <c r="E33" s="0" t="inlineStr">
         <is>
-          <t>battle_start@battle_start.xlsx</t>
+          <t>标签定义@J-标签表.xlsx</t>
         </is>
       </c>
       <c r="F33" s="0" t="inlineStr">
         <is>
-          <t>RowId</t>
+          <t>Id</t>
         </is>
       </c>
       <c r="H33" s="0" t="inlineStr">
@@ -2217,19 +2245,19 @@
       </c>
       <c r="K33" s="0" t="inlineStr">
         <is>
-          <t>battle_start</t>
+          <t>tag_definitions</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="0" t="inlineStr">
         <is>
-          <t>ResourceCharacterHfsm</t>
+          <t>TagRuleGroups</t>
         </is>
       </c>
       <c r="C34" s="0" t="inlineStr">
         <is>
-          <t>DRResourceCharacterHfsm</t>
+          <t>DRTagRuleGroups</t>
         </is>
       </c>
       <c r="D34" s="0" t="b">
@@ -2237,12 +2265,12 @@
       </c>
       <c r="E34" s="0" t="inlineStr">
         <is>
-          <t>character_hfsm@character_hfsm.xlsx</t>
+          <t>标签规则组@J-标签表.xlsx</t>
         </is>
       </c>
       <c r="F34" s="0" t="inlineStr">
         <is>
-          <t>RowId</t>
+          <t>Id</t>
         </is>
       </c>
       <c r="H34" s="0" t="inlineStr">
@@ -2252,19 +2280,19 @@
       </c>
       <c r="K34" s="0" t="inlineStr">
         <is>
-          <t>character_hfsm</t>
+          <t>tag_rule_groups</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="0" t="inlineStr">
         <is>
-          <t>ResourceCharacterViewActions</t>
+          <t>TagRuleNodes</t>
         </is>
       </c>
       <c r="C35" s="0" t="inlineStr">
         <is>
-          <t>DRResourceCharacterViewActions</t>
+          <t>DRTagRuleNodes</t>
         </is>
       </c>
       <c r="D35" s="0" t="b">
@@ -2272,12 +2300,12 @@
       </c>
       <c r="E35" s="0" t="inlineStr">
         <is>
-          <t>character_view_actions@character_view_actions.xlsx</t>
+          <t>标签规则节点@J-标签表.xlsx</t>
         </is>
       </c>
       <c r="F35" s="0" t="inlineStr">
         <is>
-          <t>RowId</t>
+          <t>Id</t>
         </is>
       </c>
       <c r="H35" s="0" t="inlineStr">
@@ -2287,19 +2315,19 @@
       </c>
       <c r="K35" s="0" t="inlineStr">
         <is>
-          <t>character_view_actions</t>
+          <t>tag_rule_nodes</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="0" t="inlineStr">
         <is>
-          <t>ResourceDemoTbitem</t>
+          <t>TagResultFlags</t>
         </is>
       </c>
       <c r="C36" s="0" t="inlineStr">
         <is>
-          <t>DRResourceDemoTbitem</t>
+          <t>DRTagResultFlags</t>
         </is>
       </c>
       <c r="D36" s="0" t="b">
@@ -2307,12 +2335,12 @@
       </c>
       <c r="E36" s="0" t="inlineStr">
         <is>
-          <t>demo_tbitem@demo_tbitem.xlsx</t>
+          <t>结果标志定义@J-标签表.xlsx</t>
         </is>
       </c>
       <c r="F36" s="0" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>Id</t>
         </is>
       </c>
       <c r="H36" s="0" t="inlineStr">
@@ -2322,19 +2350,19 @@
       </c>
       <c r="K36" s="0" t="inlineStr">
         <is>
-          <t>demo_tbitem</t>
+          <t>tag_result_flags</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="0" t="inlineStr">
         <is>
-          <t>ResourceDtbuff</t>
+          <t>TagResultMappings</t>
         </is>
       </c>
       <c r="C37" s="0" t="inlineStr">
         <is>
-          <t>DRResourceDtbuff</t>
+          <t>DRTagResultMappings</t>
         </is>
       </c>
       <c r="D37" s="0" t="b">
@@ -2342,7 +2370,7 @@
       </c>
       <c r="E37" s="0" t="inlineStr">
         <is>
-          <t>dtbuff@dtbuff.xlsx</t>
+          <t>标签结果映射@J-标签表.xlsx</t>
         </is>
       </c>
       <c r="F37" s="0" t="inlineStr">
@@ -2357,19 +2385,19 @@
       </c>
       <c r="K37" s="0" t="inlineStr">
         <is>
-          <t>dtbuff</t>
+          <t>tag_result_mappings</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="0" t="inlineStr">
         <is>
-          <t>ResourceEffectPlans</t>
+          <t>ContinuousTagTemplates</t>
         </is>
       </c>
       <c r="C38" s="0" t="inlineStr">
         <is>
-          <t>DRResourceEffectPlans</t>
+          <t>DRContinuousTagTemplates</t>
         </is>
       </c>
       <c r="D38" s="0" t="b">
@@ -2377,12 +2405,12 @@
       </c>
       <c r="E38" s="0" t="inlineStr">
         <is>
-          <t>effect_plans@effect_plans.xlsx</t>
+          <t>持续标签模板@J-标签表.xlsx</t>
         </is>
       </c>
       <c r="F38" s="0" t="inlineStr">
         <is>
-          <t>RowId</t>
+          <t>Id</t>
         </is>
       </c>
       <c r="H38" s="0" t="inlineStr">
@@ -2392,19 +2420,19 @@
       </c>
       <c r="K38" s="0" t="inlineStr">
         <is>
-          <t>effect_plans</t>
+          <t>continuous_tag_templates</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="B39" s="0" t="inlineStr">
         <is>
-          <t>ResourceOngoingEffects</t>
+          <t>ModifierParameters</t>
         </is>
       </c>
       <c r="C39" s="0" t="inlineStr">
         <is>
-          <t>DRResourceOngoingEffects</t>
+          <t>DRModifierParameters</t>
         </is>
       </c>
       <c r="D39" s="0" t="b">
@@ -2412,7 +2440,7 @@
       </c>
       <c r="E39" s="0" t="inlineStr">
         <is>
-          <t>ongoing_effects@ongoing_effects.xlsx</t>
+          <t>修饰参数@J-效果表.xlsx</t>
         </is>
       </c>
       <c r="F39" s="0" t="inlineStr">
@@ -2427,42 +2455,42 @@
       </c>
       <c r="K39" s="0" t="inlineStr">
         <is>
-          <t>ongoing_effects</t>
+          <t>modifier_parameters</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="B40" s="0" t="inlineStr">
-        <is>
-          <t>AbilityNodes</t>
-        </is>
-      </c>
-      <c r="C40" s="0" t="inlineStr">
-        <is>
-          <t>DRAbilityNodes</t>
-        </is>
-      </c>
-      <c r="D40" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E40" s="0" t="inlineStr">
-        <is>
-          <t>ability_nodes@ability_nodes.xlsx</t>
-        </is>
-      </c>
-      <c r="F40" s="0" t="inlineStr">
-        <is>
-          <t>Id</t>
-        </is>
-      </c>
-      <c r="H40" s="0" t="inlineStr">
-        <is>
-          <t>c,s,e</t>
-        </is>
-      </c>
-      <c r="K40" s="0" t="inlineStr">
-        <is>
-          <t>ability_nodes</t>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>TagBehaviorGates</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>DRTagBehaviorGates</t>
+        </is>
+      </c>
+      <c r="D40" t="b">
+        <v>1</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>行为门禁@J-标签表.xlsx</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>c,s,e</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>tag_behavior_gates</t>
         </is>
       </c>
     </row>

--- a/LubanConfig/Moba/Production/Datas/__tables__.xlsx
+++ b/LubanConfig/Moba/Production/Datas/__tables__.xlsx
@@ -1023,7 +1023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K40"/>
+  <dimension ref="A1:K42"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5"/>
   <cols>
     <col width="20.375" customWidth="1" style="3" min="2" max="2"/>
@@ -2460,37 +2460,113 @@
       </c>
     </row>
     <row r="40">
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="0" t="inlineStr">
         <is>
           <t>TagBehaviorGates</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" s="0" t="inlineStr">
         <is>
           <t>DRTagBehaviorGates</t>
         </is>
       </c>
-      <c r="D40" t="b">
-        <v>1</v>
-      </c>
-      <c r="E40" t="inlineStr">
+      <c r="D40" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E40" s="0" t="inlineStr">
         <is>
           <t>行为门禁@J-标签表.xlsx</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Id</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>c,s,e</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
+      <c r="F40" s="0" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
+      <c r="H40" s="0" t="inlineStr">
+        <is>
+          <t>c,s,e</t>
+        </is>
+      </c>
+      <c r="K40" s="0" t="inlineStr">
         <is>
           <t>tag_behavior_gates</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="0" t="inlineStr">
+        <is>
+          <t>Dungeons</t>
+        </is>
+      </c>
+      <c r="C41" s="0" t="inlineStr">
+        <is>
+          <t>DRDungeons</t>
+        </is>
+      </c>
+      <c r="D41" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E41" s="0" t="inlineStr">
+        <is>
+          <t>副本@J-战斗场景表.xlsx</t>
+        </is>
+      </c>
+      <c r="F41" s="0" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
+      <c r="H41" s="0" t="inlineStr">
+        <is>
+          <t>c,s,e</t>
+        </is>
+      </c>
+      <c r="K41" s="0" t="inlineStr">
+        <is>
+          <t>dungeons</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="0" t="n"/>
+      <c r="B42" s="0" t="inlineStr">
+        <is>
+          <t>ModifierDefinitions</t>
+        </is>
+      </c>
+      <c r="C42" s="0" t="inlineStr">
+        <is>
+          <t>DRModifierDefinitions</t>
+        </is>
+      </c>
+      <c r="D42" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E42" s="0" t="inlineStr">
+        <is>
+          <t>修饰效果定义@J-效果表.xlsx</t>
+        </is>
+      </c>
+      <c r="F42" s="0" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>c,s,e</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>修饰器语义定义：目标、运算、幅值与叠加/冲突策略</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>modifier_definitions</t>
         </is>
       </c>
     </row>

--- a/LubanConfig/Moba/Production/Datas/__tables__.xlsx
+++ b/LubanConfig/Moba/Production/Datas/__tables__.xlsx
@@ -1023,7 +1023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K42"/>
+  <dimension ref="A1:K43"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5"/>
   <cols>
     <col width="20.375" customWidth="1" style="3" min="2" max="2"/>
@@ -2554,19 +2554,59 @@
           <t>Id</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>c,s,e</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
+      <c r="H42" s="0" t="inlineStr">
+        <is>
+          <t>c,s,e</t>
+        </is>
+      </c>
+      <c r="I42" s="0" t="inlineStr">
         <is>
           <t>修饰器语义定义：目标、运算、幅值与叠加/冲突策略</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="K42" s="0" t="inlineStr">
         <is>
           <t>modifier_definitions</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>BuffHudTemplates</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>DRBuffHudTemplates</t>
+        </is>
+      </c>
+      <c r="D43" t="b">
+        <v>1</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>BuffHud@moba-buff-hud.xlsx</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>c,s,e</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Buff HUD display configuration.</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>buff_hud_templates</t>
         </is>
       </c>
     </row>

--- a/LubanConfig/Moba/Production/Datas/__tables__.xlsx
+++ b/LubanConfig/Moba/Production/Datas/__tables__.xlsx
@@ -1023,7 +1023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K43"/>
+  <dimension ref="A1:K44"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5"/>
   <cols>
     <col width="20.375" customWidth="1" style="3" min="2" max="2"/>
@@ -2571,42 +2571,82 @@
       </c>
     </row>
     <row r="43">
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="0" t="inlineStr">
         <is>
           <t>BuffHudTemplates</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C43" s="0" t="inlineStr">
         <is>
           <t>DRBuffHudTemplates</t>
         </is>
       </c>
-      <c r="D43" t="b">
-        <v>1</v>
-      </c>
-      <c r="E43" t="inlineStr">
+      <c r="D43" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E43" s="0" t="inlineStr">
         <is>
           <t>BuffHud@moba-buff-hud.xlsx</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Id</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>c,s,e</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
+      <c r="F43" s="0" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
+      <c r="H43" s="0" t="inlineStr">
+        <is>
+          <t>c,s,e</t>
+        </is>
+      </c>
+      <c r="I43" s="0" t="inlineStr">
         <is>
           <t>Buff HUD display configuration.</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="K43" s="0" t="inlineStr">
         <is>
           <t>buff_hud_templates</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>TagHudPresentations</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>DRTagHudPresentations</t>
+        </is>
+      </c>
+      <c r="D44" t="b">
+        <v>1</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>TagHudPresentations@moba-tag-hud.xlsx</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>DefinitionId</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>c,s,e</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Gameplay tag status presentation channels.</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>tag_hud_presentations</t>
         </is>
       </c>
     </row>
